--- a/Result/profitability/5205.xlsx
+++ b/Result/profitability/5205.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.21</v>
+        <v>-0.2375</v>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>2.525</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.2</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.02125000000000002</v>
+        <v>-0.02249999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>4.0625</v>
+        <v>3.1625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.92</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2837499999999999</v>
+        <v>0.25875</v>
       </c>
       <c r="N4" t="n">
-        <v>4.65375</v>
+        <v>6.393750000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.11</v>
       </c>
       <c r="M5" t="n">
-        <v>0.46375</v>
+        <v>0.4375</v>
       </c>
       <c r="N5" t="n">
-        <v>7.86125</v>
+        <v>8.693750000000001</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.45</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52625</v>
       </c>
       <c r="N6" t="n">
-        <v>10.06625</v>
+        <v>8.28125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.38</v>
       </c>
       <c r="M7" t="n">
-        <v>0.64</v>
+        <v>0.63875</v>
       </c>
       <c r="N7" t="n">
-        <v>9.745000000000001</v>
+        <v>9.42375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0.73625</v>
+        <v>0.715</v>
       </c>
       <c r="N8" t="n">
-        <v>10.855</v>
+        <v>9.0075</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0.24</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7387499999999999</v>
+        <v>0.73875</v>
       </c>
       <c r="N10" t="n">
         <v>10.61875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5205</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>8</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-87.74%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.39375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1.25625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4722222222222223</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-14.78</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-1.076474872541879</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.8638132295719845</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
